--- a/customer_satisfaction_evaluation_forms/021_customer_service_responsiveness_evaluation_form--customer_satisfaction_evaluation_forms.xlsx
+++ b/customer_satisfaction_evaluation_forms/021_customer_service_responsiveness_evaluation_form--customer_satisfaction_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,36 +525,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>customer_service_responsiveness_form</t>
+          <t>How would you rate the interaction with our customer service representative?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_service_interaction</t>
+          <t>customer_service_satisfaction_rating</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_service_interaction</t>
+          <t>On a scale of 1 to 5, how would you rate your satisfaction with our customer service?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,64 +566,64 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction</t>
+          <t>customer_service_satisfaction_reasons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>customer_satisfaction</t>
+          <t>What were the reasons for your satisfaction with our customer service?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>customer_service_responded_time</t>
+          <t>customer_service_responsiveness</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>customer_service_responded_time</t>
+          <t>How responsive was our customer service representative?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_service_response</t>
+          <t>customer_service_responded_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>customer_service_response</t>
+          <t>What was the time taken by our customer service representative to respond to your issue?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,455 +635,294 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_service_responded_time_range</t>
+          <t>customer_service_satisfaction_impact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>customer_service_responded_time_range</t>
+          <t>On a scale of 1 to 5, how would you rate the impact of our customer service on your satisfaction with our company?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>customer_service_interaction_satisfaction</t>
+          <t>customer_service_responded_time_range</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>customer_service_interaction_satisfaction</t>
+          <t>What was the range of time taken by our customer service representative to respond to your issue?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction_impact</t>
+          <t>customer_service_satisfactions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>customer_satisfaction_impact</t>
+          <t>How would you rate your overall satisfaction with our customer service?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>customer_service_responsiveness</t>
+          <t>customer_satisfaction_impact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>customer_responsiveness</t>
+          <t>What was the impact of our customer service on your satisfaction?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction_rating</t>
+          <t>customer_service_responded_time_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>customer_satisfaction_rating</t>
+          <t>Customer Service Responded Time 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction_reasons</t>
+          <t>customer_service_responsiveness_form_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>customer_satisfaction_reasons</t>
+          <t>Customer Service Responsiveness Form 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>customer_satisfaction_reasons</t>
+          <t>customer_service_responsiveness_form_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>customer_satisfaction_reasons</t>
+          <t>Would you rate our customer service responsiveness?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>customer_service_satisfactions</t>
+          <t>customer_service_satisfactions_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>customer_service_satisfactions</t>
+          <t>How would you rate our customer service responsiveness?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction_impact</t>
+          <t>customer_satisfactions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>customer_satisfaction_impact</t>
+          <t>Customer Satisfactions</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>customer_service_responsiveness</t>
+          <t>customer_service_response</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>customer_service_responsiveness</t>
+          <t>Customer Service Response</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>customer_service_responded_time</t>
+          <t>customer_service_satisfaction</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>customer_service_responded_time</t>
+          <t>Customer Service Satisfaction</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>customer_service_response</t>
+          <t>customer_service_satisfactions_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>customer_service_response</t>
+          <t>Customer Service Satisfactions 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction</t>
+          <t>customer_service_responded_time_range_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>customer_satisfaction</t>
+          <t>Customer Service Responded Time Range 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>customer_service_responded_time_range</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>customer_service_responded_time_range</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>customer_service_responsiveness_form</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>customer_service_responsiveness_form</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>customer_service_satisfactions</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>customer_satisfactions</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>customer_service_interaction</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>customer_interaction</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_impact</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_impact</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>customer_satisfactions</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>customer_satisfactions</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>customer_service_responded_time</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>customer_service_responded_time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,221 +965,221 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_service_response_choices</t>
+          <t>customer_service_responsiveness_form_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_good',_'value':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good', 'value': 'very_good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_service_response_choices</t>
+          <t>customer_service_responsiveness_form_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>customer_service_response_choices</t>
+          <t>customer_service_responsiveness_form_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 'average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_service_response_choices</t>
+          <t>customer_service_responsiveness_form_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'bad',_'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Bad', 'value': 'bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>customer_service_responded_time_range_choices</t>
+          <t>customer_service_satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_1_minute',_'value':_'less_than_1_minute'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 1 minute', 'value': 'less_than_1_minute'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>customer_service_responded_time_range_choices</t>
+          <t>customer_service_satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'1-5_minutes',_'value':_'one_to_five_minutes'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '1-5 minutes', 'value': 'one_to_five_minutes'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>customer_service_responded_time_range_choices</t>
+          <t>customer_service_satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_5_minutes',_'value':_'more_than_5_minutes'}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'More than 5 minutes', 'value': 'more_than_5_minutes'}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>customer_service_interaction_satisfaction_choices</t>
+          <t>customer_service_satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'very_good',_'value':_'very_good'}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good', 'value': 'very_good'}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>customer_service_interaction_satisfaction_choices</t>
+          <t>customer_service_satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 'good'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>customer_service_interaction_satisfaction_choices</t>
+          <t>customer_service_responsiveness_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_'average'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 'average'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>customer_service_interaction_satisfaction_choices</t>
+          <t>customer_service_responsiveness_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'bad',_'value':_'bad'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Bad', 'value': 'bad'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction_impact_choices</t>
+          <t>customer_service_responsiveness_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'strong',_'value':_'strong'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Strong', 'value': 'strong'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction_impact_choices</t>
+          <t>customer_service_responsiveness_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat',_'value':_'somewhat'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat', 'value': 'somewhat'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1352,233 +1191,692 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all', 'value': 'not_at_all'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>customer_service_responsiveness_choices</t>
+          <t>customer_service_satisfaction_impact_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_good',_'value':_'very_good'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good', 'value': 'very_good'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>customer_service_responsiveness_choices</t>
+          <t>customer_service_satisfaction_impact_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 'good'}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>customer_service_responsiveness_choices</t>
+          <t>customer_service_satisfaction_impact_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_'average'}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 'average'}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>customer_service_responsiveness_choices</t>
+          <t>customer_service_satisfaction_impact_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'bad',_'value':_'bad'}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Bad', 'value': 'bad'}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction_rating_choices</t>
+          <t>customer_service_satisfactions_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_1,_'value':_1}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 1, 'value': 1}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction_rating_choices</t>
+          <t>customer_service_satisfactions_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_2,_'value':_2}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 2, 'value': 2}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction_rating_choices</t>
+          <t>customer_service_satisfactions_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_3,_'value':_3}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 3, 'value': 3}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction_rating_choices</t>
+          <t>customer_service_satisfactions_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_4,_'value':_4}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 4, 'value': 4}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>customer_service_satisfaction_rating_choices</t>
+          <t>customer_service_responsiveness_form_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>customer_service_satisfactions_choices</t>
+          <t>customer_service_responsiveness_form_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'very_good',_'value':_'very_good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good', 'value': 'very_good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>customer_service_satisfactions_choices</t>
+          <t>customer_service_responsiveness_form_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 'good'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>customer_service_satisfactions_choices</t>
+          <t>customer_service_responsiveness_form_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_'average'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 'average'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>customer_service_satisfactions_choices</t>
+          <t>customer_service_responsiveness_form_3_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'bad',_'value':_'bad'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Bad', 'value': 'bad'}</t>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>customer_service_responsiveness_form_3_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>customer_service_responsiveness_form_3_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>customer_service_responsiveness_form_3_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>customer_service_satisfactions_2_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>very_good</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>customer_service_satisfactions_2_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>customer_service_satisfactions_2_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>customer_service_satisfactions_2_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>customer_satisfactions_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>very_good</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>customer_satisfactions_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>customer_satisfactions_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>customer_satisfactions_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>customer_service_response_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>very_good</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>customer_service_response_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>customer_service_response_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>customer_service_response_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>customer_service_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>very_good</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>customer_service_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>customer_service_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>customer_service_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>customer_service_satisfactions_3_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>very_good</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>customer_service_satisfactions_3_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>customer_service_satisfactions_3_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>customer_service_satisfactions_3_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>customer_service_responded_time_range_2_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>very_good</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>customer_service_responded_time_range_2_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>customer_service_responded_time_range_2_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>customer_service_responded_time_range_2_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bad</t>
         </is>
       </c>
     </row>
